--- a/tdxAppData/tdxIndexsBLK.xlsx
+++ b/tdxAppData/tdxIndexsBLK.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="12345"/>
+    <workbookView windowWidth="28125" windowHeight="12345"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3278,7 +3278,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3289,13 +3289,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3763,46 +3756,49 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3814,97 +3810,94 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4261,6 +4254,13 @@
   <sheetPr/>
   <dimension ref="A1:E538"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="11.625" customWidth="1"/>
+    <col min="2" max="2" width="13.25" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="5.375" customWidth="1"/>
+    <col min="5" max="5" width="7.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">

--- a/tdxAppData/tdxIndexsBLK.xlsx
+++ b/tdxAppData/tdxIndexsBLK.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12345"/>
+    <workbookView windowWidth="20490" windowHeight="7950"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2153" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2149" uniqueCount="1082">
   <si>
     <t>IndexCode</t>
   </si>
@@ -203,12 +203,6 @@
   </si>
   <si>
     <t>创业创新</t>
-  </si>
-  <si>
-    <t>399262</t>
-  </si>
-  <si>
-    <t>数字经济</t>
   </si>
   <si>
     <t>399269</t>
@@ -3278,7 +3272,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3289,6 +3283,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3756,49 +3757,46 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3810,94 +3808,97 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4252,7 +4253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E538"/>
+  <dimension ref="A1:E537"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.625" customWidth="1"/>
@@ -4766,7 +4767,7 @@
         <v>7</v>
       </c>
       <c r="D30">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -4783,7 +4784,7 @@
         <v>7</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -4885,7 +4886,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>50</v>
+        <v>2000</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -4902,7 +4903,7 @@
         <v>7</v>
       </c>
       <c r="D38">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -4936,7 +4937,7 @@
         <v>7</v>
       </c>
       <c r="D40">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -4970,7 +4971,7 @@
         <v>7</v>
       </c>
       <c r="D42">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -5004,7 +5005,7 @@
         <v>7</v>
       </c>
       <c r="D44">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -5055,7 +5056,7 @@
         <v>7</v>
       </c>
       <c r="D47">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -5106,7 +5107,7 @@
         <v>7</v>
       </c>
       <c r="D50">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -5123,7 +5124,7 @@
         <v>7</v>
       </c>
       <c r="D51">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -5140,7 +5141,7 @@
         <v>7</v>
       </c>
       <c r="D52">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -5157,7 +5158,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -5191,7 +5192,7 @@
         <v>7</v>
       </c>
       <c r="D55">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -5208,7 +5209,7 @@
         <v>7</v>
       </c>
       <c r="D56">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -5225,7 +5226,7 @@
         <v>7</v>
       </c>
       <c r="D57">
-        <v>45</v>
+        <v>332</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -5259,7 +5260,7 @@
         <v>7</v>
       </c>
       <c r="D59">
-        <v>332</v>
+        <v>66</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -5293,7 +5294,7 @@
         <v>7</v>
       </c>
       <c r="D61">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -5327,7 +5328,7 @@
         <v>7</v>
       </c>
       <c r="D63">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -5361,7 +5362,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -5378,7 +5379,7 @@
         <v>7</v>
       </c>
       <c r="D66">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -5412,7 +5413,7 @@
         <v>7</v>
       </c>
       <c r="D68">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -5446,7 +5447,7 @@
         <v>7</v>
       </c>
       <c r="D70">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -5463,7 +5464,7 @@
         <v>7</v>
       </c>
       <c r="D71">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -5480,7 +5481,7 @@
         <v>7</v>
       </c>
       <c r="D72">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -5497,7 +5498,7 @@
         <v>7</v>
       </c>
       <c r="D73">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -5511,10 +5512,10 @@
         <v>152</v>
       </c>
       <c r="C74" t="s">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="D74">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -5522,16 +5523,16 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B75" t="s">
+        <v>155</v>
+      </c>
+      <c r="C75" t="s">
         <v>153</v>
       </c>
-      <c r="B75" t="s">
-        <v>154</v>
-      </c>
-      <c r="C75" t="s">
-        <v>155</v>
-      </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -5545,10 +5546,10 @@
         <v>157</v>
       </c>
       <c r="C76" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -5556,16 +5557,16 @@
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B77" t="s">
+        <v>160</v>
+      </c>
+      <c r="C77" t="s">
         <v>158</v>
       </c>
-      <c r="B77" t="s">
-        <v>159</v>
-      </c>
-      <c r="C77" t="s">
-        <v>160</v>
-      </c>
       <c r="D77">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -5579,10 +5580,10 @@
         <v>162</v>
       </c>
       <c r="C78" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D78">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -5596,10 +5597,10 @@
         <v>164</v>
       </c>
       <c r="C79" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D79">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -5613,10 +5614,10 @@
         <v>166</v>
       </c>
       <c r="C80" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D80">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -5630,10 +5631,10 @@
         <v>168</v>
       </c>
       <c r="C81" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D81">
-        <v>87</v>
+        <v>11</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -5647,10 +5648,10 @@
         <v>170</v>
       </c>
       <c r="C82" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D82">
-        <v>11</v>
+        <v>469</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -5664,10 +5665,10 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D83">
-        <v>470</v>
+        <v>78</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -5681,10 +5682,10 @@
         <v>174</v>
       </c>
       <c r="C84" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D84">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -5698,10 +5699,10 @@
         <v>176</v>
       </c>
       <c r="C85" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D85">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -5715,10 +5716,10 @@
         <v>178</v>
       </c>
       <c r="C86" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D86">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -5732,10 +5733,10 @@
         <v>180</v>
       </c>
       <c r="C87" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D87">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -5749,10 +5750,10 @@
         <v>182</v>
       </c>
       <c r="C88" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D88">
-        <v>441</v>
+        <v>111</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -5766,10 +5767,10 @@
         <v>184</v>
       </c>
       <c r="C89" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D89">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -5783,10 +5784,10 @@
         <v>186</v>
       </c>
       <c r="C90" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D90">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -5800,10 +5801,10 @@
         <v>188</v>
       </c>
       <c r="C91" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D91">
-        <v>303</v>
+        <v>427</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -5817,10 +5818,10 @@
         <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D92">
-        <v>427</v>
+        <v>40</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -5834,10 +5835,10 @@
         <v>192</v>
       </c>
       <c r="C93" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D93">
-        <v>40</v>
+        <v>415</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -5851,10 +5852,10 @@
         <v>194</v>
       </c>
       <c r="C94" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D94">
-        <v>416</v>
+        <v>141</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -5868,10 +5869,10 @@
         <v>196</v>
       </c>
       <c r="C95" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D95">
-        <v>141</v>
+        <v>172</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -5885,10 +5886,10 @@
         <v>198</v>
       </c>
       <c r="C96" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D96">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -5902,10 +5903,10 @@
         <v>200</v>
       </c>
       <c r="C97" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D97">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -5919,10 +5920,10 @@
         <v>202</v>
       </c>
       <c r="C98" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D98">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -5936,10 +5937,10 @@
         <v>204</v>
       </c>
       <c r="C99" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D99">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -5953,10 +5954,10 @@
         <v>206</v>
       </c>
       <c r="C100" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D100">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -5970,10 +5971,10 @@
         <v>208</v>
       </c>
       <c r="C101" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D101">
-        <v>75</v>
+        <v>674</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -5987,10 +5988,10 @@
         <v>210</v>
       </c>
       <c r="C102" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D102">
-        <v>676</v>
+        <v>42</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -6004,10 +6005,10 @@
         <v>212</v>
       </c>
       <c r="C103" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D103">
-        <v>42</v>
+        <v>685</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -6021,10 +6022,10 @@
         <v>214</v>
       </c>
       <c r="C104" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D104">
-        <v>684</v>
+        <v>37</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -6038,10 +6039,10 @@
         <v>216</v>
       </c>
       <c r="C105" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D105">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -6055,10 +6056,10 @@
         <v>218</v>
       </c>
       <c r="C106" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D106">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -6072,10 +6073,10 @@
         <v>220</v>
       </c>
       <c r="C107" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D107">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -6089,10 +6090,10 @@
         <v>222</v>
       </c>
       <c r="C108" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="D108">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -6100,16 +6101,16 @@
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B109" t="s">
+        <v>225</v>
+      </c>
+      <c r="C109" t="s">
         <v>223</v>
       </c>
-      <c r="B109" t="s">
-        <v>224</v>
-      </c>
-      <c r="C109" t="s">
-        <v>225</v>
-      </c>
       <c r="D109">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -6123,10 +6124,10 @@
         <v>227</v>
       </c>
       <c r="C110" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D110">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -6140,10 +6141,10 @@
         <v>229</v>
       </c>
       <c r="C111" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D111">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -6157,10 +6158,10 @@
         <v>231</v>
       </c>
       <c r="C112" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D112">
-        <v>57</v>
+        <v>130</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -6174,10 +6175,10 @@
         <v>233</v>
       </c>
       <c r="C113" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D113">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -6191,10 +6192,10 @@
         <v>235</v>
       </c>
       <c r="C114" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D114">
-        <v>30</v>
+        <v>407</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -6208,10 +6209,10 @@
         <v>237</v>
       </c>
       <c r="C115" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D115">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -6225,10 +6226,10 @@
         <v>239</v>
       </c>
       <c r="C116" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D116">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -6242,7 +6243,7 @@
         <v>241</v>
       </c>
       <c r="C117" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D117">
         <v>32</v>
@@ -6259,10 +6260,10 @@
         <v>243</v>
       </c>
       <c r="C118" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D118">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -6276,10 +6277,10 @@
         <v>245</v>
       </c>
       <c r="C119" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D119">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -6293,10 +6294,10 @@
         <v>247</v>
       </c>
       <c r="C120" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D120">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -6310,10 +6311,10 @@
         <v>249</v>
       </c>
       <c r="C121" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D121">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -6327,10 +6328,10 @@
         <v>251</v>
       </c>
       <c r="C122" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D122">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>
@@ -6344,10 +6345,10 @@
         <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D123">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="E123" t="s">
         <v>8</v>
@@ -6361,10 +6362,10 @@
         <v>255</v>
       </c>
       <c r="C124" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D124">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="E124" t="s">
         <v>8</v>
@@ -6378,10 +6379,10 @@
         <v>257</v>
       </c>
       <c r="C125" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D125">
-        <v>269</v>
+        <v>169</v>
       </c>
       <c r="E125" t="s">
         <v>8</v>
@@ -6395,10 +6396,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D126">
-        <v>169</v>
+        <v>65</v>
       </c>
       <c r="E126" t="s">
         <v>8</v>
@@ -6412,10 +6413,10 @@
         <v>261</v>
       </c>
       <c r="C127" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D127">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="E127" t="s">
         <v>8</v>
@@ -6429,10 +6430,10 @@
         <v>263</v>
       </c>
       <c r="C128" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D128">
-        <v>297</v>
+        <v>106</v>
       </c>
       <c r="E128" t="s">
         <v>8</v>
@@ -6446,10 +6447,10 @@
         <v>265</v>
       </c>
       <c r="C129" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D129">
-        <v>106</v>
+        <v>19</v>
       </c>
       <c r="E129" t="s">
         <v>8</v>
@@ -6463,10 +6464,10 @@
         <v>267</v>
       </c>
       <c r="C130" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D130">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E130" t="s">
         <v>8</v>
@@ -6480,10 +6481,10 @@
         <v>269</v>
       </c>
       <c r="C131" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D131">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E131" t="s">
         <v>8</v>
@@ -6497,10 +6498,10 @@
         <v>271</v>
       </c>
       <c r="C132" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D132">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E132" t="s">
         <v>8</v>
@@ -6514,10 +6515,10 @@
         <v>273</v>
       </c>
       <c r="C133" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D133">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
         <v>8</v>
@@ -6531,10 +6532,10 @@
         <v>275</v>
       </c>
       <c r="C134" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E134" t="s">
         <v>8</v>
@@ -6548,10 +6549,10 @@
         <v>277</v>
       </c>
       <c r="C135" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D135">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="E135" t="s">
         <v>8</v>
@@ -6565,10 +6566,10 @@
         <v>279</v>
       </c>
       <c r="C136" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D136">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E136" t="s">
         <v>8</v>
@@ -6582,10 +6583,10 @@
         <v>281</v>
       </c>
       <c r="C137" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D137">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="E137" t="s">
         <v>8</v>
@@ -6599,10 +6600,10 @@
         <v>283</v>
       </c>
       <c r="C138" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D138">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="E138" t="s">
         <v>8</v>
@@ -6616,10 +6617,10 @@
         <v>285</v>
       </c>
       <c r="C139" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D139">
-        <v>145</v>
+        <v>285</v>
       </c>
       <c r="E139" t="s">
         <v>8</v>
@@ -6633,10 +6634,10 @@
         <v>287</v>
       </c>
       <c r="C140" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D140">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="E140" t="s">
         <v>8</v>
@@ -6650,10 +6651,10 @@
         <v>289</v>
       </c>
       <c r="C141" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D141">
-        <v>313</v>
+        <v>32</v>
       </c>
       <c r="E141" t="s">
         <v>8</v>
@@ -6667,10 +6668,10 @@
         <v>291</v>
       </c>
       <c r="C142" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D142">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E142" t="s">
         <v>8</v>
@@ -6684,10 +6685,10 @@
         <v>293</v>
       </c>
       <c r="C143" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D143">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="E143" t="s">
         <v>8</v>
@@ -6701,7 +6702,7 @@
         <v>295</v>
       </c>
       <c r="C144" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D144">
         <v>6</v>
@@ -6718,10 +6719,10 @@
         <v>297</v>
       </c>
       <c r="C145" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D145">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E145" t="s">
         <v>8</v>
@@ -6735,10 +6736,10 @@
         <v>299</v>
       </c>
       <c r="C146" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D146">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E146" t="s">
         <v>8</v>
@@ -6752,10 +6753,10 @@
         <v>301</v>
       </c>
       <c r="C147" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D147">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="E147" t="s">
         <v>8</v>
@@ -6769,10 +6770,10 @@
         <v>303</v>
       </c>
       <c r="C148" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D148">
-        <v>132</v>
+        <v>33</v>
       </c>
       <c r="E148" t="s">
         <v>8</v>
@@ -6786,10 +6787,10 @@
         <v>305</v>
       </c>
       <c r="C149" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D149">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
@@ -6803,10 +6804,10 @@
         <v>307</v>
       </c>
       <c r="C150" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D150">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E150" t="s">
         <v>8</v>
@@ -6820,10 +6821,10 @@
         <v>309</v>
       </c>
       <c r="C151" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D151">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E151" t="s">
         <v>8</v>
@@ -6837,10 +6838,10 @@
         <v>311</v>
       </c>
       <c r="C152" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D152">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="E152" t="s">
         <v>8</v>
@@ -6854,10 +6855,10 @@
         <v>313</v>
       </c>
       <c r="C153" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D153">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
         <v>8</v>
@@ -6871,10 +6872,10 @@
         <v>315</v>
       </c>
       <c r="C154" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D154">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E154" t="s">
         <v>8</v>
@@ -6888,10 +6889,10 @@
         <v>317</v>
       </c>
       <c r="C155" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D155">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="E155" t="s">
         <v>8</v>
@@ -6905,10 +6906,10 @@
         <v>319</v>
       </c>
       <c r="C156" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D156">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="E156" t="s">
         <v>8</v>
@@ -6922,10 +6923,10 @@
         <v>321</v>
       </c>
       <c r="C157" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D157">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="E157" t="s">
         <v>8</v>
@@ -6939,10 +6940,10 @@
         <v>323</v>
       </c>
       <c r="C158" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D158">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="E158" t="s">
         <v>8</v>
@@ -6956,10 +6957,10 @@
         <v>325</v>
       </c>
       <c r="C159" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D159">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E159" t="s">
         <v>8</v>
@@ -6973,10 +6974,10 @@
         <v>327</v>
       </c>
       <c r="C160" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D160">
-        <v>162</v>
+        <v>276</v>
       </c>
       <c r="E160" t="s">
         <v>8</v>
@@ -6990,10 +6991,10 @@
         <v>329</v>
       </c>
       <c r="C161" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D161">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E161" t="s">
         <v>8</v>
@@ -7007,10 +7008,10 @@
         <v>331</v>
       </c>
       <c r="C162" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D162">
-        <v>292</v>
+        <v>88</v>
       </c>
       <c r="E162" t="s">
         <v>8</v>
@@ -7024,10 +7025,10 @@
         <v>333</v>
       </c>
       <c r="C163" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D163">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
@@ -7041,10 +7042,10 @@
         <v>335</v>
       </c>
       <c r="C164" t="s">
-        <v>225</v>
+        <v>336</v>
       </c>
       <c r="D164">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="E164" t="s">
         <v>8</v>
@@ -7052,16 +7053,16 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B165" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C165" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D165">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="E165" t="s">
         <v>8</v>
@@ -7075,10 +7076,10 @@
         <v>340</v>
       </c>
       <c r="C166" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D166">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E166" t="s">
         <v>8</v>
@@ -7092,10 +7093,10 @@
         <v>342</v>
       </c>
       <c r="C167" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D167">
-        <v>62</v>
+        <v>339</v>
       </c>
       <c r="E167" t="s">
         <v>8</v>
@@ -7109,10 +7110,10 @@
         <v>344</v>
       </c>
       <c r="C168" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D168">
-        <v>338</v>
+        <v>389</v>
       </c>
       <c r="E168" t="s">
         <v>8</v>
@@ -7126,10 +7127,10 @@
         <v>346</v>
       </c>
       <c r="C169" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D169">
-        <v>389</v>
+        <v>78</v>
       </c>
       <c r="E169" t="s">
         <v>8</v>
@@ -7143,10 +7144,10 @@
         <v>348</v>
       </c>
       <c r="C170" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D170">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
@@ -7160,10 +7161,10 @@
         <v>350</v>
       </c>
       <c r="C171" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D171">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="E171" t="s">
         <v>8</v>
@@ -7177,10 +7178,10 @@
         <v>352</v>
       </c>
       <c r="C172" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D172">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E172" t="s">
         <v>8</v>
@@ -7194,10 +7195,10 @@
         <v>354</v>
       </c>
       <c r="C173" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D173">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E173" t="s">
         <v>8</v>
@@ -7211,10 +7212,10 @@
         <v>356</v>
       </c>
       <c r="C174" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D174">
-        <v>158</v>
+        <v>53</v>
       </c>
       <c r="E174" t="s">
         <v>8</v>
@@ -7228,10 +7229,10 @@
         <v>358</v>
       </c>
       <c r="C175" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D175">
-        <v>53</v>
+        <v>497</v>
       </c>
       <c r="E175" t="s">
         <v>8</v>
@@ -7245,10 +7246,10 @@
         <v>360</v>
       </c>
       <c r="C176" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D176">
-        <v>499</v>
+        <v>114</v>
       </c>
       <c r="E176" t="s">
         <v>8</v>
@@ -7262,10 +7263,10 @@
         <v>362</v>
       </c>
       <c r="C177" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D177">
-        <v>114</v>
+        <v>424</v>
       </c>
       <c r="E177" t="s">
         <v>8</v>
@@ -7279,10 +7280,10 @@
         <v>364</v>
       </c>
       <c r="C178" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D178">
-        <v>425</v>
+        <v>91</v>
       </c>
       <c r="E178" t="s">
         <v>8</v>
@@ -7296,10 +7297,10 @@
         <v>366</v>
       </c>
       <c r="C179" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D179">
-        <v>91</v>
+        <v>303</v>
       </c>
       <c r="E179" t="s">
         <v>8</v>
@@ -7313,10 +7314,10 @@
         <v>368</v>
       </c>
       <c r="C180" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D180">
-        <v>302</v>
+        <v>370</v>
       </c>
       <c r="E180" t="s">
         <v>8</v>
@@ -7330,10 +7331,10 @@
         <v>370</v>
       </c>
       <c r="C181" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D181">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="E181" t="s">
         <v>8</v>
@@ -7347,10 +7348,10 @@
         <v>372</v>
       </c>
       <c r="C182" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D182">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="E182" t="s">
         <v>8</v>
@@ -7364,10 +7365,10 @@
         <v>374</v>
       </c>
       <c r="C183" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D183">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="E183" t="s">
         <v>8</v>
@@ -7381,10 +7382,10 @@
         <v>376</v>
       </c>
       <c r="C184" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D184">
-        <v>179</v>
+        <v>56</v>
       </c>
       <c r="E184" t="s">
         <v>8</v>
@@ -7398,10 +7399,10 @@
         <v>378</v>
       </c>
       <c r="C185" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D185">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="E185" t="s">
         <v>8</v>
@@ -7415,10 +7416,10 @@
         <v>380</v>
       </c>
       <c r="C186" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D186">
-        <v>279</v>
+        <v>110</v>
       </c>
       <c r="E186" t="s">
         <v>8</v>
@@ -7432,10 +7433,10 @@
         <v>382</v>
       </c>
       <c r="C187" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D187">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="E187" t="s">
         <v>8</v>
@@ -7449,10 +7450,10 @@
         <v>384</v>
       </c>
       <c r="C188" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D188">
-        <v>41</v>
+        <v>395</v>
       </c>
       <c r="E188" t="s">
         <v>8</v>
@@ -7466,10 +7467,10 @@
         <v>386</v>
       </c>
       <c r="C189" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D189">
-        <v>395</v>
+        <v>203</v>
       </c>
       <c r="E189" t="s">
         <v>8</v>
@@ -7483,10 +7484,10 @@
         <v>388</v>
       </c>
       <c r="C190" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D190">
-        <v>203</v>
+        <v>88</v>
       </c>
       <c r="E190" t="s">
         <v>8</v>
@@ -7500,10 +7501,10 @@
         <v>390</v>
       </c>
       <c r="C191" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D191">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="E191" t="s">
         <v>8</v>
@@ -7517,10 +7518,10 @@
         <v>392</v>
       </c>
       <c r="C192" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D192">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E192" t="s">
         <v>8</v>
@@ -7534,10 +7535,10 @@
         <v>394</v>
       </c>
       <c r="C193" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D193">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="E193" t="s">
         <v>8</v>
@@ -7551,10 +7552,10 @@
         <v>396</v>
       </c>
       <c r="C194" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D194">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="E194" t="s">
         <v>8</v>
@@ -7568,10 +7569,10 @@
         <v>398</v>
       </c>
       <c r="C195" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D195">
-        <v>169</v>
+        <v>7</v>
       </c>
       <c r="E195" t="s">
         <v>8</v>
@@ -7585,10 +7586,10 @@
         <v>400</v>
       </c>
       <c r="C196" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D196">
-        <v>7</v>
+        <v>204</v>
       </c>
       <c r="E196" t="s">
         <v>8</v>
@@ -7602,10 +7603,10 @@
         <v>402</v>
       </c>
       <c r="C197" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D197">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c r="E197" t="s">
         <v>8</v>
@@ -7619,7 +7620,7 @@
         <v>404</v>
       </c>
       <c r="C198" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D198">
         <v>40</v>
@@ -7636,10 +7637,10 @@
         <v>406</v>
       </c>
       <c r="C199" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D199">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E199" t="s">
         <v>8</v>
@@ -7653,10 +7654,10 @@
         <v>408</v>
       </c>
       <c r="C200" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D200">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E200" t="s">
         <v>8</v>
@@ -7670,10 +7671,10 @@
         <v>410</v>
       </c>
       <c r="C201" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D201">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E201" t="s">
         <v>8</v>
@@ -7687,10 +7688,10 @@
         <v>412</v>
       </c>
       <c r="C202" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D202">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E202" t="s">
         <v>8</v>
@@ -7704,10 +7705,10 @@
         <v>414</v>
       </c>
       <c r="C203" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D203">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E203" t="s">
         <v>8</v>
@@ -7721,10 +7722,10 @@
         <v>416</v>
       </c>
       <c r="C204" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D204">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="E204" t="s">
         <v>8</v>
@@ -7738,10 +7739,10 @@
         <v>418</v>
       </c>
       <c r="C205" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D205">
-        <v>34</v>
+        <v>205</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
@@ -7755,10 +7756,10 @@
         <v>420</v>
       </c>
       <c r="C206" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D206">
-        <v>205</v>
+        <v>48</v>
       </c>
       <c r="E206" t="s">
         <v>8</v>
@@ -7772,10 +7773,10 @@
         <v>422</v>
       </c>
       <c r="C207" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D207">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="E207" t="s">
         <v>8</v>
@@ -7789,10 +7790,10 @@
         <v>424</v>
       </c>
       <c r="C208" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D208">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="E208" t="s">
         <v>8</v>
@@ -7806,10 +7807,10 @@
         <v>426</v>
       </c>
       <c r="C209" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D209">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="E209" t="s">
         <v>8</v>
@@ -7823,10 +7824,10 @@
         <v>428</v>
       </c>
       <c r="C210" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D210">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="E210" t="s">
         <v>8</v>
@@ -7840,10 +7841,10 @@
         <v>430</v>
       </c>
       <c r="C211" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D211">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="E211" t="s">
         <v>8</v>
@@ -7857,10 +7858,10 @@
         <v>432</v>
       </c>
       <c r="C212" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D212">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="E212" t="s">
         <v>8</v>
@@ -7874,10 +7875,10 @@
         <v>434</v>
       </c>
       <c r="C213" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D213">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E213" t="s">
         <v>8</v>
@@ -7891,10 +7892,10 @@
         <v>436</v>
       </c>
       <c r="C214" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D214">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E214" t="s">
         <v>8</v>
@@ -7908,10 +7909,10 @@
         <v>438</v>
       </c>
       <c r="C215" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D215">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="E215" t="s">
         <v>8</v>
@@ -7925,10 +7926,10 @@
         <v>440</v>
       </c>
       <c r="C216" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D216">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E216" t="s">
         <v>8</v>
@@ -7942,10 +7943,10 @@
         <v>442</v>
       </c>
       <c r="C217" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D217">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="E217" t="s">
         <v>8</v>
@@ -7959,10 +7960,10 @@
         <v>444</v>
       </c>
       <c r="C218" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D218">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E218" t="s">
         <v>8</v>
@@ -7976,10 +7977,10 @@
         <v>446</v>
       </c>
       <c r="C219" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D219">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="E219" t="s">
         <v>8</v>
@@ -7993,10 +7994,10 @@
         <v>448</v>
       </c>
       <c r="C220" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D220">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E220" t="s">
         <v>8</v>
@@ -8010,10 +8011,10 @@
         <v>450</v>
       </c>
       <c r="C221" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D221">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E221" t="s">
         <v>8</v>
@@ -8027,10 +8028,10 @@
         <v>452</v>
       </c>
       <c r="C222" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D222">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="E222" t="s">
         <v>8</v>
@@ -8044,10 +8045,10 @@
         <v>454</v>
       </c>
       <c r="C223" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D223">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="E223" t="s">
         <v>8</v>
@@ -8061,10 +8062,10 @@
         <v>456</v>
       </c>
       <c r="C224" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D224">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="E224" t="s">
         <v>8</v>
@@ -8078,10 +8079,10 @@
         <v>458</v>
       </c>
       <c r="C225" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D225">
-        <v>127</v>
+        <v>398</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
@@ -8095,10 +8096,10 @@
         <v>460</v>
       </c>
       <c r="C226" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D226">
-        <v>398</v>
+        <v>74</v>
       </c>
       <c r="E226" t="s">
         <v>8</v>
@@ -8112,10 +8113,10 @@
         <v>462</v>
       </c>
       <c r="C227" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D227">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E227" t="s">
         <v>8</v>
@@ -8129,10 +8130,10 @@
         <v>464</v>
       </c>
       <c r="C228" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D228">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E228" t="s">
         <v>8</v>
@@ -8146,10 +8147,10 @@
         <v>466</v>
       </c>
       <c r="C229" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D229">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E229" t="s">
         <v>8</v>
@@ -8163,10 +8164,10 @@
         <v>468</v>
       </c>
       <c r="C230" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D230">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E230" t="s">
         <v>8</v>
@@ -8180,10 +8181,10 @@
         <v>470</v>
       </c>
       <c r="C231" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D231">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E231" t="s">
         <v>8</v>
@@ -8197,10 +8198,10 @@
         <v>472</v>
       </c>
       <c r="C232" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D232">
-        <v>30</v>
+        <v>122</v>
       </c>
       <c r="E232" t="s">
         <v>8</v>
@@ -8214,10 +8215,10 @@
         <v>474</v>
       </c>
       <c r="C233" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D233">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="E233" t="s">
         <v>8</v>
@@ -8231,10 +8232,10 @@
         <v>476</v>
       </c>
       <c r="C234" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D234">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="E234" t="s">
         <v>8</v>
@@ -8248,10 +8249,10 @@
         <v>478</v>
       </c>
       <c r="C235" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D235">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E235" t="s">
         <v>8</v>
@@ -8265,10 +8266,10 @@
         <v>480</v>
       </c>
       <c r="C236" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D236">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="E236" t="s">
         <v>8</v>
@@ -8282,10 +8283,10 @@
         <v>482</v>
       </c>
       <c r="C237" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D237">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="E237" t="s">
         <v>8</v>
@@ -8299,10 +8300,10 @@
         <v>484</v>
       </c>
       <c r="C238" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D238">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="E238" t="s">
         <v>8</v>
@@ -8316,10 +8317,10 @@
         <v>486</v>
       </c>
       <c r="C239" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D239">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E239" t="s">
         <v>8</v>
@@ -8333,10 +8334,10 @@
         <v>488</v>
       </c>
       <c r="C240" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D240">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="E240" t="s">
         <v>8</v>
@@ -8350,10 +8351,10 @@
         <v>490</v>
       </c>
       <c r="C241" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D241">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="E241" t="s">
         <v>8</v>
@@ -8367,10 +8368,10 @@
         <v>492</v>
       </c>
       <c r="C242" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D242">
-        <v>100</v>
+        <v>29</v>
       </c>
       <c r="E242" t="s">
         <v>8</v>
@@ -8384,10 +8385,10 @@
         <v>494</v>
       </c>
       <c r="C243" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D243">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E243" t="s">
         <v>8</v>
@@ -8401,10 +8402,10 @@
         <v>496</v>
       </c>
       <c r="C244" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D244">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E244" t="s">
         <v>8</v>
@@ -8418,10 +8419,10 @@
         <v>498</v>
       </c>
       <c r="C245" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D245">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="E245" t="s">
         <v>8</v>
@@ -8435,10 +8436,10 @@
         <v>500</v>
       </c>
       <c r="C246" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D246">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="E246" t="s">
         <v>8</v>
@@ -8452,10 +8453,10 @@
         <v>502</v>
       </c>
       <c r="C247" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D247">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="E247" t="s">
         <v>8</v>
@@ -8469,10 +8470,10 @@
         <v>504</v>
       </c>
       <c r="C248" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D248">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="E248" t="s">
         <v>8</v>
@@ -8486,10 +8487,10 @@
         <v>506</v>
       </c>
       <c r="C249" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D249">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E249" t="s">
         <v>8</v>
@@ -8503,10 +8504,10 @@
         <v>508</v>
       </c>
       <c r="C250" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D250">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E250" t="s">
         <v>8</v>
@@ -8520,10 +8521,10 @@
         <v>510</v>
       </c>
       <c r="C251" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D251">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
@@ -8537,10 +8538,10 @@
         <v>512</v>
       </c>
       <c r="C252" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D252">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="E252" t="s">
         <v>8</v>
@@ -8554,10 +8555,10 @@
         <v>514</v>
       </c>
       <c r="C253" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D253">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E253" t="s">
         <v>8</v>
@@ -8571,10 +8572,10 @@
         <v>516</v>
       </c>
       <c r="C254" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D254">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E254" t="s">
         <v>8</v>
@@ -8588,10 +8589,10 @@
         <v>518</v>
       </c>
       <c r="C255" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D255">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="E255" t="s">
         <v>8</v>
@@ -8605,10 +8606,10 @@
         <v>520</v>
       </c>
       <c r="C256" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D256">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="E256" t="s">
         <v>8</v>
@@ -8622,10 +8623,10 @@
         <v>522</v>
       </c>
       <c r="C257" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D257">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="E257" t="s">
         <v>8</v>
@@ -8639,10 +8640,10 @@
         <v>524</v>
       </c>
       <c r="C258" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D258">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="E258" t="s">
         <v>8</v>
@@ -8656,10 +8657,10 @@
         <v>526</v>
       </c>
       <c r="C259" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D259">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E259" t="s">
         <v>8</v>
@@ -8673,10 +8674,10 @@
         <v>528</v>
       </c>
       <c r="C260" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D260">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="E260" t="s">
         <v>8</v>
@@ -8690,10 +8691,10 @@
         <v>530</v>
       </c>
       <c r="C261" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D261">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E261" t="s">
         <v>8</v>
@@ -8707,10 +8708,10 @@
         <v>532</v>
       </c>
       <c r="C262" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D262">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E262" t="s">
         <v>8</v>
@@ -8724,10 +8725,10 @@
         <v>534</v>
       </c>
       <c r="C263" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D263">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="E263" t="s">
         <v>8</v>
@@ -8741,10 +8742,10 @@
         <v>536</v>
       </c>
       <c r="C264" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D264">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="E264" t="s">
         <v>8</v>
@@ -8758,10 +8759,10 @@
         <v>538</v>
       </c>
       <c r="C265" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D265">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E265" t="s">
         <v>8</v>
@@ -8775,10 +8776,10 @@
         <v>540</v>
       </c>
       <c r="C266" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D266">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E266" t="s">
         <v>8</v>
@@ -8792,10 +8793,10 @@
         <v>542</v>
       </c>
       <c r="C267" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D267">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="E267" t="s">
         <v>8</v>
@@ -8809,10 +8810,10 @@
         <v>544</v>
       </c>
       <c r="C268" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D268">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="E268" t="s">
         <v>8</v>
@@ -8826,10 +8827,10 @@
         <v>546</v>
       </c>
       <c r="C269" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D269">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E269" t="s">
         <v>8</v>
@@ -8843,10 +8844,10 @@
         <v>548</v>
       </c>
       <c r="C270" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D270">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E270" t="s">
         <v>8</v>
@@ -8860,10 +8861,10 @@
         <v>550</v>
       </c>
       <c r="C271" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D271">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E271" t="s">
         <v>8</v>
@@ -8877,10 +8878,10 @@
         <v>552</v>
       </c>
       <c r="C272" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D272">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E272" t="s">
         <v>8</v>
@@ -8894,10 +8895,10 @@
         <v>554</v>
       </c>
       <c r="C273" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D273">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E273" t="s">
         <v>8</v>
@@ -8911,10 +8912,10 @@
         <v>556</v>
       </c>
       <c r="C274" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D274">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="E274" t="s">
         <v>8</v>
@@ -8928,10 +8929,10 @@
         <v>558</v>
       </c>
       <c r="C275" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D275">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="E275" t="s">
         <v>8</v>
@@ -8945,10 +8946,10 @@
         <v>560</v>
       </c>
       <c r="C276" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D276">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="E276" t="s">
         <v>8</v>
@@ -8962,10 +8963,10 @@
         <v>562</v>
       </c>
       <c r="C277" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D277">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E277" t="s">
         <v>8</v>
@@ -8979,10 +8980,10 @@
         <v>564</v>
       </c>
       <c r="C278" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D278">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E278" t="s">
         <v>8</v>
@@ -8996,10 +8997,10 @@
         <v>566</v>
       </c>
       <c r="C279" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D279">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E279" t="s">
         <v>8</v>
@@ -9013,10 +9014,10 @@
         <v>568</v>
       </c>
       <c r="C280" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D280">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E280" t="s">
         <v>8</v>
@@ -9030,10 +9031,10 @@
         <v>570</v>
       </c>
       <c r="C281" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D281">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="E281" t="s">
         <v>8</v>
@@ -9047,10 +9048,10 @@
         <v>572</v>
       </c>
       <c r="C282" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D282">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="E282" t="s">
         <v>8</v>
@@ -9064,10 +9065,10 @@
         <v>574</v>
       </c>
       <c r="C283" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D283">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="E283" t="s">
         <v>8</v>
@@ -9081,10 +9082,10 @@
         <v>576</v>
       </c>
       <c r="C284" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D284">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E284" t="s">
         <v>8</v>
@@ -9098,10 +9099,10 @@
         <v>578</v>
       </c>
       <c r="C285" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D285">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E285" t="s">
         <v>8</v>
@@ -9115,10 +9116,10 @@
         <v>580</v>
       </c>
       <c r="C286" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D286">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E286" t="s">
         <v>8</v>
@@ -9132,10 +9133,10 @@
         <v>582</v>
       </c>
       <c r="C287" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D287">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="E287" t="s">
         <v>8</v>
@@ -9149,10 +9150,10 @@
         <v>584</v>
       </c>
       <c r="C288" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D288">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E288" t="s">
         <v>8</v>
@@ -9166,10 +9167,10 @@
         <v>586</v>
       </c>
       <c r="C289" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D289">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E289" t="s">
         <v>8</v>
@@ -9183,7 +9184,7 @@
         <v>588</v>
       </c>
       <c r="C290" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D290">
         <v>41</v>
@@ -9200,10 +9201,10 @@
         <v>590</v>
       </c>
       <c r="C291" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D291">
-        <v>41</v>
+        <v>125</v>
       </c>
       <c r="E291" t="s">
         <v>8</v>
@@ -9217,7 +9218,7 @@
         <v>592</v>
       </c>
       <c r="C292" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D292">
         <v>125</v>
@@ -9234,10 +9235,10 @@
         <v>594</v>
       </c>
       <c r="C293" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D293">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="E293" t="s">
         <v>8</v>
@@ -9251,10 +9252,10 @@
         <v>596</v>
       </c>
       <c r="C294" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D294">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="E294" t="s">
         <v>8</v>
@@ -9268,10 +9269,10 @@
         <v>598</v>
       </c>
       <c r="C295" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D295">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="E295" t="s">
         <v>8</v>
@@ -9285,10 +9286,10 @@
         <v>600</v>
       </c>
       <c r="C296" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D296">
-        <v>94</v>
+        <v>23</v>
       </c>
       <c r="E296" t="s">
         <v>8</v>
@@ -9302,10 +9303,10 @@
         <v>602</v>
       </c>
       <c r="C297" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D297">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="E297" t="s">
         <v>8</v>
@@ -9319,10 +9320,10 @@
         <v>604</v>
       </c>
       <c r="C298" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D298">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E298" t="s">
         <v>8</v>
@@ -9336,10 +9337,10 @@
         <v>606</v>
       </c>
       <c r="C299" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D299">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E299" t="s">
         <v>8</v>
@@ -9353,10 +9354,10 @@
         <v>608</v>
       </c>
       <c r="C300" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D300">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="E300" t="s">
         <v>8</v>
@@ -9370,10 +9371,10 @@
         <v>610</v>
       </c>
       <c r="C301" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D301">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E301" t="s">
         <v>8</v>
@@ -9387,10 +9388,10 @@
         <v>612</v>
       </c>
       <c r="C302" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D302">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E302" t="s">
         <v>8</v>
@@ -9404,10 +9405,10 @@
         <v>614</v>
       </c>
       <c r="C303" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D303">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E303" t="s">
         <v>8</v>
@@ -9421,10 +9422,10 @@
         <v>616</v>
       </c>
       <c r="C304" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D304">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E304" t="s">
         <v>8</v>
@@ -9438,10 +9439,10 @@
         <v>618</v>
       </c>
       <c r="C305" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D305">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E305" t="s">
         <v>8</v>
@@ -9455,10 +9456,10 @@
         <v>620</v>
       </c>
       <c r="C306" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D306">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="E306" t="s">
         <v>8</v>
@@ -9472,10 +9473,10 @@
         <v>622</v>
       </c>
       <c r="C307" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D307">
-        <v>198</v>
+        <v>19</v>
       </c>
       <c r="E307" t="s">
         <v>8</v>
@@ -9489,10 +9490,10 @@
         <v>624</v>
       </c>
       <c r="C308" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D308">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E308" t="s">
         <v>8</v>
@@ -9506,10 +9507,10 @@
         <v>626</v>
       </c>
       <c r="C309" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D309">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E309" t="s">
         <v>8</v>
@@ -9523,10 +9524,10 @@
         <v>628</v>
       </c>
       <c r="C310" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D310">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E310" t="s">
         <v>8</v>
@@ -9540,10 +9541,10 @@
         <v>630</v>
       </c>
       <c r="C311" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D311">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="E311" t="s">
         <v>8</v>
@@ -9557,10 +9558,10 @@
         <v>632</v>
       </c>
       <c r="C312" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D312">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="E312" t="s">
         <v>8</v>
@@ -9574,10 +9575,10 @@
         <v>634</v>
       </c>
       <c r="C313" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D313">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="E313" t="s">
         <v>8</v>
@@ -9591,10 +9592,10 @@
         <v>636</v>
       </c>
       <c r="C314" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D314">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E314" t="s">
         <v>8</v>
@@ -9608,10 +9609,10 @@
         <v>638</v>
       </c>
       <c r="C315" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D315">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="E315" t="s">
         <v>8</v>
@@ -9625,10 +9626,10 @@
         <v>640</v>
       </c>
       <c r="C316" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D316">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E316" t="s">
         <v>8</v>
@@ -9642,7 +9643,7 @@
         <v>642</v>
       </c>
       <c r="C317" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D317">
         <v>36</v>
@@ -9659,10 +9660,10 @@
         <v>644</v>
       </c>
       <c r="C318" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D318">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E318" t="s">
         <v>8</v>
@@ -9676,10 +9677,10 @@
         <v>646</v>
       </c>
       <c r="C319" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D319">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E319" t="s">
         <v>8</v>
@@ -9693,7 +9694,7 @@
         <v>648</v>
       </c>
       <c r="C320" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D320">
         <v>100</v>
@@ -9710,10 +9711,10 @@
         <v>650</v>
       </c>
       <c r="C321" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D321">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="E321" t="s">
         <v>8</v>
@@ -9727,10 +9728,10 @@
         <v>652</v>
       </c>
       <c r="C322" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D322">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="E322" t="s">
         <v>8</v>
@@ -9744,10 +9745,10 @@
         <v>654</v>
       </c>
       <c r="C323" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D323">
-        <v>175</v>
+        <v>64</v>
       </c>
       <c r="E323" t="s">
         <v>8</v>
@@ -9761,10 +9762,10 @@
         <v>656</v>
       </c>
       <c r="C324" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D324">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E324" t="s">
         <v>8</v>
@@ -9778,10 +9779,10 @@
         <v>658</v>
       </c>
       <c r="C325" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D325">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="E325" t="s">
         <v>8</v>
@@ -9795,10 +9796,10 @@
         <v>660</v>
       </c>
       <c r="C326" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D326">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E326" t="s">
         <v>8</v>
@@ -9812,10 +9813,10 @@
         <v>662</v>
       </c>
       <c r="C327" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D327">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E327" t="s">
         <v>8</v>
@@ -9829,10 +9830,10 @@
         <v>664</v>
       </c>
       <c r="C328" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D328">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E328" t="s">
         <v>8</v>
@@ -9846,10 +9847,10 @@
         <v>666</v>
       </c>
       <c r="C329" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D329">
-        <v>40</v>
+        <v>303</v>
       </c>
       <c r="E329" t="s">
         <v>8</v>
@@ -9863,10 +9864,10 @@
         <v>668</v>
       </c>
       <c r="C330" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D330">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="E330" t="s">
         <v>8</v>
@@ -9880,10 +9881,10 @@
         <v>670</v>
       </c>
       <c r="C331" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D331">
-        <v>334</v>
+        <v>28</v>
       </c>
       <c r="E331" t="s">
         <v>8</v>
@@ -9897,10 +9898,10 @@
         <v>672</v>
       </c>
       <c r="C332" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D332">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E332" t="s">
         <v>8</v>
@@ -9914,10 +9915,10 @@
         <v>674</v>
       </c>
       <c r="C333" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D333">
-        <v>26</v>
+        <v>657</v>
       </c>
       <c r="E333" t="s">
         <v>8</v>
@@ -9931,10 +9932,10 @@
         <v>676</v>
       </c>
       <c r="C334" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D334">
-        <v>657</v>
+        <v>66</v>
       </c>
       <c r="E334" t="s">
         <v>8</v>
@@ -9948,10 +9949,10 @@
         <v>678</v>
       </c>
       <c r="C335" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D335">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="E335" t="s">
         <v>8</v>
@@ -9965,10 +9966,10 @@
         <v>680</v>
       </c>
       <c r="C336" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D336">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="E336" t="s">
         <v>8</v>
@@ -9982,10 +9983,10 @@
         <v>682</v>
       </c>
       <c r="C337" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D337">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="E337" t="s">
         <v>8</v>
@@ -9999,10 +10000,10 @@
         <v>684</v>
       </c>
       <c r="C338" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D338">
-        <v>128</v>
+        <v>48</v>
       </c>
       <c r="E338" t="s">
         <v>8</v>
@@ -10016,10 +10017,10 @@
         <v>686</v>
       </c>
       <c r="C339" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D339">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="E339" t="s">
         <v>8</v>
@@ -10033,10 +10034,10 @@
         <v>688</v>
       </c>
       <c r="C340" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D340">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="E340" t="s">
         <v>8</v>
@@ -10050,10 +10051,10 @@
         <v>690</v>
       </c>
       <c r="C341" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D341">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E341" t="s">
         <v>8</v>
@@ -10067,10 +10068,10 @@
         <v>692</v>
       </c>
       <c r="C342" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D342">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E342" t="s">
         <v>8</v>
@@ -10084,10 +10085,10 @@
         <v>694</v>
       </c>
       <c r="C343" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D343">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E343" t="s">
         <v>8</v>
@@ -10101,10 +10102,10 @@
         <v>696</v>
       </c>
       <c r="C344" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D344">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E344" t="s">
         <v>8</v>
@@ -10118,10 +10119,10 @@
         <v>698</v>
       </c>
       <c r="C345" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D345">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="E345" t="s">
         <v>8</v>
@@ -10135,10 +10136,10 @@
         <v>700</v>
       </c>
       <c r="C346" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D346">
-        <v>152</v>
+        <v>30</v>
       </c>
       <c r="E346" t="s">
         <v>8</v>
@@ -10152,10 +10153,10 @@
         <v>702</v>
       </c>
       <c r="C347" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D347">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="E347" t="s">
         <v>8</v>
@@ -10169,10 +10170,10 @@
         <v>704</v>
       </c>
       <c r="C348" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D348">
-        <v>128</v>
+        <v>6</v>
       </c>
       <c r="E348" t="s">
         <v>8</v>
@@ -10186,10 +10187,10 @@
         <v>706</v>
       </c>
       <c r="C349" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D349">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E349" t="s">
         <v>8</v>
@@ -10200,13 +10201,13 @@
         <v>707</v>
       </c>
       <c r="B350" t="s">
-        <v>708</v>
+        <v>136</v>
       </c>
       <c r="C350" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D350">
-        <v>7</v>
+        <v>178</v>
       </c>
       <c r="E350" t="s">
         <v>8</v>
@@ -10214,16 +10215,16 @@
     </row>
     <row r="351" spans="1:5">
       <c r="A351" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B351" t="s">
         <v>709</v>
       </c>
-      <c r="B351" t="s">
-        <v>138</v>
-      </c>
       <c r="C351" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D351">
-        <v>178</v>
+        <v>14</v>
       </c>
       <c r="E351" t="s">
         <v>8</v>
@@ -10237,10 +10238,10 @@
         <v>711</v>
       </c>
       <c r="C352" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D352">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E352" t="s">
         <v>8</v>
@@ -10254,10 +10255,10 @@
         <v>713</v>
       </c>
       <c r="C353" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D353">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E353" t="s">
         <v>8</v>
@@ -10271,10 +10272,10 @@
         <v>715</v>
       </c>
       <c r="C354" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D354">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="E354" t="s">
         <v>8</v>
@@ -10288,10 +10289,10 @@
         <v>717</v>
       </c>
       <c r="C355" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D355">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="E355" t="s">
         <v>8</v>
@@ -10305,10 +10306,10 @@
         <v>719</v>
       </c>
       <c r="C356" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D356">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E356" t="s">
         <v>8</v>
@@ -10322,10 +10323,10 @@
         <v>721</v>
       </c>
       <c r="C357" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D357">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="E357" t="s">
         <v>8</v>
@@ -10339,10 +10340,10 @@
         <v>723</v>
       </c>
       <c r="C358" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D358">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="E358" t="s">
         <v>8</v>
@@ -10356,10 +10357,10 @@
         <v>725</v>
       </c>
       <c r="C359" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D359">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="E359" t="s">
         <v>8</v>
@@ -10373,10 +10374,10 @@
         <v>727</v>
       </c>
       <c r="C360" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D360">
-        <v>208</v>
+        <v>22</v>
       </c>
       <c r="E360" t="s">
         <v>8</v>
@@ -10390,10 +10391,10 @@
         <v>729</v>
       </c>
       <c r="C361" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D361">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="E361" t="s">
         <v>8</v>
@@ -10407,10 +10408,10 @@
         <v>731</v>
       </c>
       <c r="C362" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D362">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="E362" t="s">
         <v>8</v>
@@ -10424,10 +10425,10 @@
         <v>733</v>
       </c>
       <c r="C363" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D363">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="E363" t="s">
         <v>8</v>
@@ -10441,10 +10442,10 @@
         <v>735</v>
       </c>
       <c r="C364" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D364">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="E364" t="s">
         <v>8</v>
@@ -10458,10 +10459,10 @@
         <v>737</v>
       </c>
       <c r="C365" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D365">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="E365" t="s">
         <v>8</v>
@@ -10475,10 +10476,10 @@
         <v>739</v>
       </c>
       <c r="C366" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D366">
-        <v>54</v>
+        <v>263</v>
       </c>
       <c r="E366" t="s">
         <v>8</v>
@@ -10492,10 +10493,10 @@
         <v>741</v>
       </c>
       <c r="C367" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D367">
-        <v>263</v>
+        <v>22</v>
       </c>
       <c r="E367" t="s">
         <v>8</v>
@@ -10509,10 +10510,10 @@
         <v>743</v>
       </c>
       <c r="C368" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D368">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E368" t="s">
         <v>8</v>
@@ -10526,10 +10527,10 @@
         <v>745</v>
       </c>
       <c r="C369" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D369">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E369" t="s">
         <v>8</v>
@@ -10543,10 +10544,10 @@
         <v>747</v>
       </c>
       <c r="C370" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D370">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E370" t="s">
         <v>8</v>
@@ -10560,10 +10561,10 @@
         <v>749</v>
       </c>
       <c r="C371" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D371">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E371" t="s">
         <v>8</v>
@@ -10577,10 +10578,10 @@
         <v>751</v>
       </c>
       <c r="C372" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D372">
-        <v>50</v>
+        <v>377</v>
       </c>
       <c r="E372" t="s">
         <v>8</v>
@@ -10594,10 +10595,10 @@
         <v>753</v>
       </c>
       <c r="C373" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D373">
-        <v>377</v>
+        <v>156</v>
       </c>
       <c r="E373" t="s">
         <v>8</v>
@@ -10611,10 +10612,10 @@
         <v>755</v>
       </c>
       <c r="C374" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D374">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="E374" t="s">
         <v>8</v>
@@ -10628,10 +10629,10 @@
         <v>757</v>
       </c>
       <c r="C375" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D375">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="E375" t="s">
         <v>8</v>
@@ -10645,10 +10646,10 @@
         <v>759</v>
       </c>
       <c r="C376" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D376">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="E376" t="s">
         <v>8</v>
@@ -10662,10 +10663,10 @@
         <v>761</v>
       </c>
       <c r="C377" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D377">
-        <v>39</v>
+        <v>265</v>
       </c>
       <c r="E377" t="s">
         <v>8</v>
@@ -10679,10 +10680,10 @@
         <v>763</v>
       </c>
       <c r="C378" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D378">
-        <v>266</v>
+        <v>27</v>
       </c>
       <c r="E378" t="s">
         <v>8</v>
@@ -10696,10 +10697,10 @@
         <v>765</v>
       </c>
       <c r="C379" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D379">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E379" t="s">
         <v>8</v>
@@ -10713,10 +10714,10 @@
         <v>767</v>
       </c>
       <c r="C380" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D380">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="E380" t="s">
         <v>8</v>
@@ -10730,10 +10731,10 @@
         <v>769</v>
       </c>
       <c r="C381" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D381">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E381" t="s">
         <v>8</v>
@@ -10747,10 +10748,10 @@
         <v>771</v>
       </c>
       <c r="C382" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D382">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E382" t="s">
         <v>8</v>
@@ -10764,7 +10765,7 @@
         <v>773</v>
       </c>
       <c r="C383" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D383">
         <v>100</v>
@@ -10781,10 +10782,10 @@
         <v>775</v>
       </c>
       <c r="C384" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D384">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E384" t="s">
         <v>8</v>
@@ -10798,10 +10799,10 @@
         <v>777</v>
       </c>
       <c r="C385" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D385">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="E385" t="s">
         <v>8</v>
@@ -10815,10 +10816,10 @@
         <v>779</v>
       </c>
       <c r="C386" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D386">
-        <v>206</v>
+        <v>33</v>
       </c>
       <c r="E386" t="s">
         <v>8</v>
@@ -10832,7 +10833,7 @@
         <v>781</v>
       </c>
       <c r="C387" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D387">
         <v>33</v>
@@ -10849,10 +10850,10 @@
         <v>783</v>
       </c>
       <c r="C388" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D388">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E388" t="s">
         <v>8</v>
@@ -10866,10 +10867,10 @@
         <v>785</v>
       </c>
       <c r="C389" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D389">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E389" t="s">
         <v>8</v>
@@ -10883,10 +10884,10 @@
         <v>787</v>
       </c>
       <c r="C390" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D390">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="E390" t="s">
         <v>8</v>
@@ -10900,10 +10901,10 @@
         <v>789</v>
       </c>
       <c r="C391" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D391">
-        <v>47</v>
+        <v>100</v>
       </c>
       <c r="E391" t="s">
         <v>8</v>
@@ -10917,7 +10918,7 @@
         <v>791</v>
       </c>
       <c r="C392" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D392">
         <v>100</v>
@@ -10934,7 +10935,7 @@
         <v>793</v>
       </c>
       <c r="C393" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D393">
         <v>100</v>
@@ -10951,7 +10952,7 @@
         <v>795</v>
       </c>
       <c r="C394" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D394">
         <v>100</v>
@@ -10968,7 +10969,7 @@
         <v>797</v>
       </c>
       <c r="C395" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D395">
         <v>100</v>
@@ -10985,7 +10986,7 @@
         <v>799</v>
       </c>
       <c r="C396" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D396">
         <v>100</v>
@@ -11002,10 +11003,10 @@
         <v>801</v>
       </c>
       <c r="C397" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D397">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E397" t="s">
         <v>8</v>
@@ -11019,10 +11020,10 @@
         <v>803</v>
       </c>
       <c r="C398" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D398">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E398" t="s">
         <v>8</v>
@@ -11036,10 +11037,10 @@
         <v>805</v>
       </c>
       <c r="C399" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D399">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E399" t="s">
         <v>8</v>
@@ -11053,10 +11054,10 @@
         <v>807</v>
       </c>
       <c r="C400" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D400">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E400" t="s">
         <v>8</v>
@@ -11070,7 +11071,7 @@
         <v>809</v>
       </c>
       <c r="C401" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D401">
         <v>50</v>
@@ -11087,10 +11088,10 @@
         <v>811</v>
       </c>
       <c r="C402" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D402">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E402" t="s">
         <v>8</v>
@@ -11104,10 +11105,10 @@
         <v>813</v>
       </c>
       <c r="C403" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D403">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E403" t="s">
         <v>8</v>
@@ -11121,10 +11122,10 @@
         <v>815</v>
       </c>
       <c r="C404" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D404">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E404" t="s">
         <v>8</v>
@@ -11138,10 +11139,10 @@
         <v>817</v>
       </c>
       <c r="C405" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D405">
-        <v>68</v>
+        <v>400</v>
       </c>
       <c r="E405" t="s">
         <v>8</v>
@@ -11155,10 +11156,10 @@
         <v>819</v>
       </c>
       <c r="C406" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D406">
-        <v>400</v>
+        <v>30</v>
       </c>
       <c r="E406" t="s">
         <v>8</v>
@@ -11172,10 +11173,10 @@
         <v>821</v>
       </c>
       <c r="C407" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D407">
-        <v>30</v>
+        <v>344</v>
       </c>
       <c r="E407" t="s">
         <v>8</v>
@@ -11189,10 +11190,10 @@
         <v>823</v>
       </c>
       <c r="C408" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D408">
-        <v>344</v>
+        <v>50</v>
       </c>
       <c r="E408" t="s">
         <v>8</v>
@@ -11206,10 +11207,10 @@
         <v>825</v>
       </c>
       <c r="C409" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D409">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E409" t="s">
         <v>8</v>
@@ -11223,10 +11224,10 @@
         <v>827</v>
       </c>
       <c r="C410" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D410">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E410" t="s">
         <v>8</v>
@@ -11240,10 +11241,10 @@
         <v>829</v>
       </c>
       <c r="C411" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D411">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="E411" t="s">
         <v>8</v>
@@ -11257,10 +11258,10 @@
         <v>831</v>
       </c>
       <c r="C412" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D412">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E412" t="s">
         <v>8</v>
@@ -11274,7 +11275,7 @@
         <v>833</v>
       </c>
       <c r="C413" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D413">
         <v>200</v>
@@ -11291,7 +11292,7 @@
         <v>835</v>
       </c>
       <c r="C414" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D414">
         <v>200</v>
@@ -11308,7 +11309,7 @@
         <v>837</v>
       </c>
       <c r="C415" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D415">
         <v>200</v>
@@ -11325,10 +11326,10 @@
         <v>839</v>
       </c>
       <c r="C416" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D416">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E416" t="s">
         <v>8</v>
@@ -11342,7 +11343,7 @@
         <v>841</v>
       </c>
       <c r="C417" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D417">
         <v>100</v>
@@ -11359,7 +11360,7 @@
         <v>843</v>
       </c>
       <c r="C418" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D418">
         <v>100</v>
@@ -11376,10 +11377,10 @@
         <v>845</v>
       </c>
       <c r="C419" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D419">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="E419" t="s">
         <v>8</v>
@@ -11393,10 +11394,10 @@
         <v>847</v>
       </c>
       <c r="C420" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D420">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="E420" t="s">
         <v>8</v>
@@ -11410,10 +11411,10 @@
         <v>849</v>
       </c>
       <c r="C421" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D421">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="E421" t="s">
         <v>8</v>
@@ -11427,10 +11428,10 @@
         <v>851</v>
       </c>
       <c r="C422" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D422">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E422" t="s">
         <v>8</v>
@@ -11444,10 +11445,10 @@
         <v>853</v>
       </c>
       <c r="C423" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D423">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="E423" t="s">
         <v>8</v>
@@ -11461,10 +11462,10 @@
         <v>855</v>
       </c>
       <c r="C424" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D424">
-        <v>200</v>
+        <v>349</v>
       </c>
       <c r="E424" t="s">
         <v>8</v>
@@ -11478,10 +11479,10 @@
         <v>857</v>
       </c>
       <c r="C425" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D425">
-        <v>368</v>
+        <v>127</v>
       </c>
       <c r="E425" t="s">
         <v>8</v>
@@ -11495,10 +11496,10 @@
         <v>859</v>
       </c>
       <c r="C426" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D426">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="E426" t="s">
         <v>8</v>
@@ -11512,10 +11513,10 @@
         <v>861</v>
       </c>
       <c r="C427" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D427">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="E427" t="s">
         <v>8</v>
@@ -11529,10 +11530,10 @@
         <v>863</v>
       </c>
       <c r="C428" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D428">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="E428" t="s">
         <v>8</v>
@@ -11546,10 +11547,10 @@
         <v>865</v>
       </c>
       <c r="C429" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D429">
-        <v>251</v>
+        <v>100</v>
       </c>
       <c r="E429" t="s">
         <v>8</v>
@@ -11563,10 +11564,10 @@
         <v>867</v>
       </c>
       <c r="C430" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D430">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E430" t="s">
         <v>8</v>
@@ -11580,10 +11581,10 @@
         <v>869</v>
       </c>
       <c r="C431" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D431">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="E431" t="s">
         <v>8</v>
@@ -11597,10 +11598,10 @@
         <v>871</v>
       </c>
       <c r="C432" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D432">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="E432" t="s">
         <v>8</v>
@@ -11614,10 +11615,10 @@
         <v>873</v>
       </c>
       <c r="C433" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D433">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="E433" t="s">
         <v>8</v>
@@ -11631,10 +11632,10 @@
         <v>875</v>
       </c>
       <c r="C434" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D434">
-        <v>183</v>
+        <v>263</v>
       </c>
       <c r="E434" t="s">
         <v>8</v>
@@ -11648,10 +11649,10 @@
         <v>877</v>
       </c>
       <c r="C435" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D435">
-        <v>263</v>
+        <v>13</v>
       </c>
       <c r="E435" t="s">
         <v>8</v>
@@ -11665,10 +11666,10 @@
         <v>879</v>
       </c>
       <c r="C436" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D436">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="E436" t="s">
         <v>8</v>
@@ -11682,10 +11683,10 @@
         <v>881</v>
       </c>
       <c r="C437" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D437">
-        <v>66</v>
+        <v>229</v>
       </c>
       <c r="E437" t="s">
         <v>8</v>
@@ -11699,10 +11700,10 @@
         <v>883</v>
       </c>
       <c r="C438" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D438">
-        <v>229</v>
+        <v>400</v>
       </c>
       <c r="E438" t="s">
         <v>8</v>
@@ -11716,10 +11717,10 @@
         <v>885</v>
       </c>
       <c r="C439" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D439">
-        <v>400</v>
+        <v>52</v>
       </c>
       <c r="E439" t="s">
         <v>8</v>
@@ -11733,10 +11734,10 @@
         <v>887</v>
       </c>
       <c r="C440" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D440">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E440" t="s">
         <v>8</v>
@@ -11750,10 +11751,10 @@
         <v>889</v>
       </c>
       <c r="C441" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D441">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="E441" t="s">
         <v>8</v>
@@ -11767,10 +11768,10 @@
         <v>891</v>
       </c>
       <c r="C442" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D442">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="E442" t="s">
         <v>8</v>
@@ -11784,10 +11785,10 @@
         <v>893</v>
       </c>
       <c r="C443" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D443">
-        <v>284</v>
+        <v>70</v>
       </c>
       <c r="E443" t="s">
         <v>8</v>
@@ -11801,10 +11802,10 @@
         <v>895</v>
       </c>
       <c r="C444" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D444">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="E444" t="s">
         <v>8</v>
@@ -11818,10 +11819,10 @@
         <v>897</v>
       </c>
       <c r="C445" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D445">
-        <v>94</v>
+        <v>229</v>
       </c>
       <c r="E445" t="s">
         <v>8</v>
@@ -11835,10 +11836,10 @@
         <v>899</v>
       </c>
       <c r="C446" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D446">
-        <v>250</v>
+        <v>442</v>
       </c>
       <c r="E446" t="s">
         <v>8</v>
@@ -11852,10 +11853,10 @@
         <v>901</v>
       </c>
       <c r="C447" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D447">
-        <v>442</v>
+        <v>119</v>
       </c>
       <c r="E447" t="s">
         <v>8</v>
@@ -11869,10 +11870,10 @@
         <v>903</v>
       </c>
       <c r="C448" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D448">
-        <v>119</v>
+        <v>12</v>
       </c>
       <c r="E448" t="s">
         <v>8</v>
@@ -11886,10 +11887,10 @@
         <v>905</v>
       </c>
       <c r="C449" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D449">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="E449" t="s">
         <v>8</v>
@@ -11903,10 +11904,10 @@
         <v>907</v>
       </c>
       <c r="C450" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D450">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E450" t="s">
         <v>8</v>
@@ -11920,10 +11921,10 @@
         <v>909</v>
       </c>
       <c r="C451" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D451">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E451" t="s">
         <v>8</v>
@@ -11937,10 +11938,10 @@
         <v>911</v>
       </c>
       <c r="C452" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D452">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E452" t="s">
         <v>8</v>
@@ -11954,7 +11955,7 @@
         <v>913</v>
       </c>
       <c r="C453" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D453">
         <v>100</v>
@@ -11971,10 +11972,10 @@
         <v>915</v>
       </c>
       <c r="C454" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D454">
-        <v>100</v>
+        <v>144</v>
       </c>
       <c r="E454" t="s">
         <v>8</v>
@@ -11988,10 +11989,10 @@
         <v>917</v>
       </c>
       <c r="C455" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D455">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="E455" t="s">
         <v>8</v>
@@ -12005,10 +12006,10 @@
         <v>919</v>
       </c>
       <c r="C456" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D456">
-        <v>268</v>
+        <v>127</v>
       </c>
       <c r="E456" t="s">
         <v>8</v>
@@ -12022,10 +12023,10 @@
         <v>921</v>
       </c>
       <c r="C457" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D457">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="E457" t="s">
         <v>8</v>
@@ -12039,10 +12040,10 @@
         <v>923</v>
       </c>
       <c r="C458" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D458">
-        <v>25</v>
+        <v>176</v>
       </c>
       <c r="E458" t="s">
         <v>8</v>
@@ -12056,10 +12057,10 @@
         <v>925</v>
       </c>
       <c r="C459" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D459">
-        <v>177</v>
+        <v>322</v>
       </c>
       <c r="E459" t="s">
         <v>8</v>
@@ -12073,10 +12074,10 @@
         <v>927</v>
       </c>
       <c r="C460" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D460">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="E460" t="s">
         <v>8</v>
@@ -12090,10 +12091,10 @@
         <v>929</v>
       </c>
       <c r="C461" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D461">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E461" t="s">
         <v>8</v>
@@ -12107,10 +12108,10 @@
         <v>931</v>
       </c>
       <c r="C462" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D462">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="E462" t="s">
         <v>8</v>
@@ -12124,10 +12125,10 @@
         <v>933</v>
       </c>
       <c r="C463" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D463">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="E463" t="s">
         <v>8</v>
@@ -12141,10 +12142,10 @@
         <v>935</v>
       </c>
       <c r="C464" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D464">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E464" t="s">
         <v>8</v>
@@ -12158,10 +12159,10 @@
         <v>937</v>
       </c>
       <c r="C465" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D465">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="E465" t="s">
         <v>8</v>
@@ -12175,10 +12176,10 @@
         <v>939</v>
       </c>
       <c r="C466" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D466">
-        <v>5</v>
+        <v>395</v>
       </c>
       <c r="E466" t="s">
         <v>8</v>
@@ -12192,10 +12193,10 @@
         <v>941</v>
       </c>
       <c r="C467" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D467">
-        <v>400</v>
+        <v>53</v>
       </c>
       <c r="E467" t="s">
         <v>8</v>
@@ -12209,10 +12210,10 @@
         <v>943</v>
       </c>
       <c r="C468" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D468">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E468" t="s">
         <v>8</v>
@@ -12226,10 +12227,10 @@
         <v>945</v>
       </c>
       <c r="C469" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D469">
-        <v>28</v>
+        <v>173</v>
       </c>
       <c r="E469" t="s">
         <v>8</v>
@@ -12243,10 +12244,10 @@
         <v>947</v>
       </c>
       <c r="C470" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D470">
-        <v>173</v>
+        <v>31</v>
       </c>
       <c r="E470" t="s">
         <v>8</v>
@@ -12260,10 +12261,10 @@
         <v>949</v>
       </c>
       <c r="C471" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D471">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E471" t="s">
         <v>8</v>
@@ -12277,10 +12278,10 @@
         <v>951</v>
       </c>
       <c r="C472" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D472">
-        <v>38</v>
+        <v>220</v>
       </c>
       <c r="E472" t="s">
         <v>8</v>
@@ -12294,10 +12295,10 @@
         <v>953</v>
       </c>
       <c r="C473" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D473">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="E473" t="s">
         <v>8</v>
@@ -12311,10 +12312,10 @@
         <v>955</v>
       </c>
       <c r="C474" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D474">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="E474" t="s">
         <v>8</v>
@@ -12328,10 +12329,10 @@
         <v>957</v>
       </c>
       <c r="C475" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D475">
-        <v>21</v>
+        <v>136</v>
       </c>
       <c r="E475" t="s">
         <v>8</v>
@@ -12345,10 +12346,10 @@
         <v>959</v>
       </c>
       <c r="C476" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D476">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="E476" t="s">
         <v>8</v>
@@ -12362,10 +12363,10 @@
         <v>961</v>
       </c>
       <c r="C477" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D477">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="E477" t="s">
         <v>8</v>
@@ -12379,10 +12380,10 @@
         <v>963</v>
       </c>
       <c r="C478" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D478">
-        <v>11</v>
+        <v>394</v>
       </c>
       <c r="E478" t="s">
         <v>8</v>
@@ -12396,10 +12397,10 @@
         <v>965</v>
       </c>
       <c r="C479" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D479">
-        <v>394</v>
+        <v>20</v>
       </c>
       <c r="E479" t="s">
         <v>8</v>
@@ -12413,10 +12414,10 @@
         <v>967</v>
       </c>
       <c r="C480" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D480">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="E480" t="s">
         <v>8</v>
@@ -12430,10 +12431,10 @@
         <v>969</v>
       </c>
       <c r="C481" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D481">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="E481" t="s">
         <v>8</v>
@@ -12447,10 +12448,10 @@
         <v>971</v>
       </c>
       <c r="C482" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D482">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="E482" t="s">
         <v>8</v>
@@ -12464,10 +12465,10 @@
         <v>973</v>
       </c>
       <c r="C483" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D483">
-        <v>177</v>
+        <v>14</v>
       </c>
       <c r="E483" t="s">
         <v>8</v>
@@ -12481,10 +12482,10 @@
         <v>975</v>
       </c>
       <c r="C484" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D484">
-        <v>14</v>
+        <v>218</v>
       </c>
       <c r="E484" t="s">
         <v>8</v>
@@ -12498,10 +12499,10 @@
         <v>977</v>
       </c>
       <c r="C485" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D485">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="E485" t="s">
         <v>8</v>
@@ -12515,10 +12516,10 @@
         <v>979</v>
       </c>
       <c r="C486" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D486">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E486" t="s">
         <v>8</v>
@@ -12532,10 +12533,10 @@
         <v>981</v>
       </c>
       <c r="C487" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D487">
-        <v>88</v>
+        <v>207</v>
       </c>
       <c r="E487" t="s">
         <v>8</v>
@@ -12549,10 +12550,10 @@
         <v>983</v>
       </c>
       <c r="C488" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D488">
-        <v>207</v>
+        <v>394</v>
       </c>
       <c r="E488" t="s">
         <v>8</v>
@@ -12566,10 +12567,10 @@
         <v>985</v>
       </c>
       <c r="C489" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D489">
-        <v>394</v>
+        <v>203</v>
       </c>
       <c r="E489" t="s">
         <v>8</v>
@@ -12583,10 +12584,10 @@
         <v>987</v>
       </c>
       <c r="C490" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D490">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="E490" t="s">
         <v>8</v>
@@ -12600,10 +12601,10 @@
         <v>989</v>
       </c>
       <c r="C491" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D491">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="E491" t="s">
         <v>8</v>
@@ -12617,10 +12618,10 @@
         <v>991</v>
       </c>
       <c r="C492" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D492">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="E492" t="s">
         <v>8</v>
@@ -12634,10 +12635,10 @@
         <v>993</v>
       </c>
       <c r="C493" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D493">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E493" t="s">
         <v>8</v>
@@ -12651,10 +12652,10 @@
         <v>995</v>
       </c>
       <c r="C494" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D494">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="E494" t="s">
         <v>8</v>
@@ -12668,10 +12669,10 @@
         <v>997</v>
       </c>
       <c r="C495" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D495">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E495" t="s">
         <v>8</v>
@@ -12685,10 +12686,10 @@
         <v>999</v>
       </c>
       <c r="C496" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D496">
-        <v>35</v>
+        <v>185</v>
       </c>
       <c r="E496" t="s">
         <v>8</v>
@@ -12702,10 +12703,10 @@
         <v>1001</v>
       </c>
       <c r="C497" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D497">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="E497" t="s">
         <v>8</v>
@@ -12719,10 +12720,10 @@
         <v>1003</v>
       </c>
       <c r="C498" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D498">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E498" t="s">
         <v>8</v>
@@ -12736,10 +12737,10 @@
         <v>1005</v>
       </c>
       <c r="C499" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D499">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E499" t="s">
         <v>8</v>
@@ -12753,10 +12754,10 @@
         <v>1007</v>
       </c>
       <c r="C500" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D500">
-        <v>31</v>
+        <v>177</v>
       </c>
       <c r="E500" t="s">
         <v>8</v>
@@ -12770,10 +12771,10 @@
         <v>1009</v>
       </c>
       <c r="C501" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D501">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="E501" t="s">
         <v>8</v>
@@ -12787,10 +12788,10 @@
         <v>1011</v>
       </c>
       <c r="C502" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D502">
-        <v>120</v>
+        <v>171</v>
       </c>
       <c r="E502" t="s">
         <v>8</v>
@@ -12804,10 +12805,10 @@
         <v>1013</v>
       </c>
       <c r="C503" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D503">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E503" t="s">
         <v>8</v>
@@ -12821,10 +12822,10 @@
         <v>1015</v>
       </c>
       <c r="C504" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D504">
-        <v>159</v>
+        <v>236</v>
       </c>
       <c r="E504" t="s">
         <v>8</v>
@@ -12838,10 +12839,10 @@
         <v>1017</v>
       </c>
       <c r="C505" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D505">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="E505" t="s">
         <v>8</v>
@@ -12855,10 +12856,10 @@
         <v>1019</v>
       </c>
       <c r="C506" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D506">
-        <v>47</v>
+        <v>128</v>
       </c>
       <c r="E506" t="s">
         <v>8</v>
@@ -12872,10 +12873,10 @@
         <v>1021</v>
       </c>
       <c r="C507" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D507">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E507" t="s">
         <v>8</v>
@@ -12889,10 +12890,10 @@
         <v>1023</v>
       </c>
       <c r="C508" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D508">
-        <v>120</v>
+        <v>237</v>
       </c>
       <c r="E508" t="s">
         <v>8</v>
@@ -12906,10 +12907,10 @@
         <v>1025</v>
       </c>
       <c r="C509" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D509">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="E509" t="s">
         <v>8</v>
@@ -12923,10 +12924,10 @@
         <v>1027</v>
       </c>
       <c r="C510" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D510">
-        <v>42</v>
+        <v>396</v>
       </c>
       <c r="E510" t="s">
         <v>8</v>
@@ -12940,10 +12941,10 @@
         <v>1029</v>
       </c>
       <c r="C511" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D511">
-        <v>396</v>
+        <v>232</v>
       </c>
       <c r="E511" t="s">
         <v>8</v>
@@ -12957,10 +12958,10 @@
         <v>1031</v>
       </c>
       <c r="C512" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D512">
-        <v>232</v>
+        <v>137</v>
       </c>
       <c r="E512" t="s">
         <v>8</v>
@@ -12974,10 +12975,10 @@
         <v>1033</v>
       </c>
       <c r="C513" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D513">
-        <v>137</v>
+        <v>392</v>
       </c>
       <c r="E513" t="s">
         <v>8</v>
@@ -12991,10 +12992,10 @@
         <v>1035</v>
       </c>
       <c r="C514" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D514">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E514" t="s">
         <v>8</v>
@@ -13008,10 +13009,10 @@
         <v>1037</v>
       </c>
       <c r="C515" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D515">
-        <v>395</v>
+        <v>30</v>
       </c>
       <c r="E515" t="s">
         <v>8</v>
@@ -13025,10 +13026,10 @@
         <v>1039</v>
       </c>
       <c r="C516" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D516">
-        <v>30</v>
+        <v>283</v>
       </c>
       <c r="E516" t="s">
         <v>8</v>
@@ -13042,10 +13043,10 @@
         <v>1041</v>
       </c>
       <c r="C517" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D517">
-        <v>282</v>
+        <v>154</v>
       </c>
       <c r="E517" t="s">
         <v>8</v>
@@ -13059,10 +13060,10 @@
         <v>1043</v>
       </c>
       <c r="C518" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D518">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E518" t="s">
         <v>8</v>
@@ -13076,10 +13077,10 @@
         <v>1045</v>
       </c>
       <c r="C519" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D519">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E519" t="s">
         <v>8</v>
@@ -13093,10 +13094,10 @@
         <v>1047</v>
       </c>
       <c r="C520" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D520">
-        <v>158</v>
+        <v>50</v>
       </c>
       <c r="E520" t="s">
         <v>8</v>
@@ -13110,10 +13111,10 @@
         <v>1049</v>
       </c>
       <c r="C521" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D521">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="E521" t="s">
         <v>8</v>
@@ -13127,10 +13128,10 @@
         <v>1051</v>
       </c>
       <c r="C522" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D522">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="E522" t="s">
         <v>8</v>
@@ -13144,10 +13145,10 @@
         <v>1053</v>
       </c>
       <c r="C523" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D523">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="E523" t="s">
         <v>8</v>
@@ -13161,10 +13162,10 @@
         <v>1055</v>
       </c>
       <c r="C524" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D524">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E524" t="s">
         <v>8</v>
@@ -13178,10 +13179,10 @@
         <v>1057</v>
       </c>
       <c r="C525" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D525">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="E525" t="s">
         <v>8</v>
@@ -13195,10 +13196,10 @@
         <v>1059</v>
       </c>
       <c r="C526" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D526">
-        <v>96</v>
+        <v>197</v>
       </c>
       <c r="E526" t="s">
         <v>8</v>
@@ -13212,10 +13213,10 @@
         <v>1061</v>
       </c>
       <c r="C527" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D527">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="E527" t="s">
         <v>8</v>
@@ -13229,10 +13230,10 @@
         <v>1063</v>
       </c>
       <c r="C528" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D528">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="E528" t="s">
         <v>8</v>
@@ -13246,10 +13247,10 @@
         <v>1065</v>
       </c>
       <c r="C529" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D529">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E529" t="s">
         <v>8</v>
@@ -13263,10 +13264,10 @@
         <v>1067</v>
       </c>
       <c r="C530" t="s">
-        <v>338</v>
+        <v>153</v>
       </c>
       <c r="D530">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E530" t="s">
         <v>8</v>
@@ -13280,10 +13281,10 @@
         <v>1069</v>
       </c>
       <c r="C531" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="D531">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E531" t="s">
         <v>8</v>
@@ -13297,10 +13298,10 @@
         <v>1071</v>
       </c>
       <c r="C532" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D532">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E532" t="s">
         <v>8</v>
@@ -13314,10 +13315,10 @@
         <v>1073</v>
       </c>
       <c r="C533" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D533">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="E533" t="s">
         <v>8</v>
@@ -13331,10 +13332,10 @@
         <v>1075</v>
       </c>
       <c r="C534" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D534">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E534" t="s">
         <v>8</v>
@@ -13348,10 +13349,10 @@
         <v>1077</v>
       </c>
       <c r="C535" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D535">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="E535" t="s">
         <v>8</v>
@@ -13365,10 +13366,10 @@
         <v>1079</v>
       </c>
       <c r="C536" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D536">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E536" t="s">
         <v>8</v>
@@ -13382,36 +13383,16 @@
         <v>1081</v>
       </c>
       <c r="C537" t="s">
-        <v>338</v>
+        <v>7</v>
       </c>
       <c r="D537">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="E537" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="538" spans="1:5">
-      <c r="A538" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B538" t="s">
-        <v>1083</v>
-      </c>
-      <c r="C538" t="s">
-        <v>7</v>
-      </c>
-      <c r="D538">
-        <v>50</v>
-      </c>
-      <c r="E538" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState ref="A2:E538">
-    <sortCondition ref="A2"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
